--- a/public/Master Buyer.xlsx
+++ b/public/Master Buyer.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>No</t>
   </si>
@@ -44,37 +44,40 @@
     <t>Buyer Contact</t>
   </si>
   <si>
-    <t>KOH001</t>
-  </si>
-  <si>
-    <t>KOHLS</t>
-  </si>
-  <si>
-    <t>JCP001</t>
+    <t>BYR000000001</t>
+  </si>
+  <si>
+    <t>KOHL'S</t>
+  </si>
+  <si>
+    <t>Menomonee Falls, Wisconsin, Amerika Serikat</t>
+  </si>
+  <si>
+    <t>BYR000000002</t>
   </si>
   <si>
     <t>JCP</t>
   </si>
   <si>
-    <t>ON001</t>
+    <t>BYR000000003</t>
   </si>
   <si>
     <t>ON</t>
   </si>
   <si>
-    <t>MUJ001</t>
+    <t>BYR000000004</t>
   </si>
   <si>
     <t>MUJI</t>
   </si>
   <si>
-    <t>AEO001</t>
+    <t>BYR000000005</t>
   </si>
   <si>
     <t>AEO</t>
   </si>
   <si>
-    <t>LEV001</t>
+    <t>BYR000000006</t>
   </si>
   <si>
     <t>LEVIS</t>
@@ -1015,6 +1018,11 @@
   <sheetPr/>
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="2" max="2" width="14.2857142857143" customWidth="1"/>
+    <col min="4" max="4" width="14.8571428571429" customWidth="1"/>
+    <col min="5" max="5" width="14.2857142857143" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
@@ -1043,7 +1051,9 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5">
@@ -1051,10 +1061,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -1064,10 +1074,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -1077,10 +1087,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -1090,10 +1100,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -1103,10 +1113,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
